--- a/public/template/template_bulk_ita_ho.xlsx
+++ b/public/template/template_bulk_ita_ho.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Kerjaan\Bjb\Aplikasi AMT\Back Office\App\Local\bulk_kosongan\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772B4B41-BFEC-4C15-B4A0-E9458F47B30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A639B69-AFC1-48BC-BC51-69FBCFEE56D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/template/template_bulk_ita_ho.xlsx
+++ b/public/template/template_bulk_ita_ho.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Kerjaan\Bjb\Aplikasi AMT\Back Office\App\Local\bulk_kosongan\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Pemograman\laragon\www\newboost\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A639B69-AFC1-48BC-BC51-69FBCFEE56D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8810ED-3222-452C-A93E-EF7C30E78E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -51,9 +54,6 @@
     <t>Suffix Account Debit</t>
   </si>
   <si>
-    <t>Reference</t>
-  </si>
-  <si>
     <t>Keterangan Debit 1</t>
   </si>
   <si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Cost Center</t>
+  </si>
+  <si>
+    <t>Refference</t>
   </si>
 </sst>
 </file>
@@ -436,15 +439,15 @@
     <col min="8" max="8" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="17.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="17.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="9.21875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -465,7 +468,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -474,31 +477,31 @@
         <v>0</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.3">
